--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260728.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260728.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>32,782</t>
+          <t>32,542</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.62%</t>
+          <t>10.31%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>79,241</t>
+          <t>78,659</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.27%</t>
+          <t>10.20%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>91,403</t>
+          <t>90,731</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.54%</t>
+          <t>8.21%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>35,979</t>
+          <t>35,715</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.25%</t>
+          <t>7.06%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>197,483</t>
+          <t>196,032</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.70%</t>
+          <t>5.88%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>105,029</t>
+          <t>104,258</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>4.53%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>113,909</t>
+          <t>113,072</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.68%</t>
         </is>
       </c>
     </row>
@@ -765,78 +765,78 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>19,610</t>
+          <t>19,466</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>49,580</t>
+          <t>59,224</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>59,662</t>
+          <t>117,609</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>118,479</t>
+          <t>49,215</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>54,874</t>
+          <t>54,471</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>137,926</t>
+          <t>136,913</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -897,56 +897,56 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>22,800</t>
+          <t>22,632</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>24,593</t>
+          <t>62,583</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>63,046</t>
+          <t>24,413</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>37,218</t>
+          <t>36,945</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>51,820</t>
+          <t>51,440</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1007,122 +1007,122 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>50,330</t>
+          <t>49,960</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>11,472</t>
+          <t>77,347</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>77,920</t>
+          <t>50,285</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>50,657</t>
+          <t>32,656</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>32,898</t>
+          <t>11,388</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>22,524</t>
+          <t>47,239</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1139,100 +1139,100 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>30,808</t>
+          <t>30,582</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>47,588</t>
+          <t>22,358</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>27,898</t>
+          <t>95,490</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>20,956</t>
+          <t>27,693</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>96,197</t>
+          <t>20,802</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -1249,29 +1249,29 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>75,970</t>
+          <t>75,412</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>4,980</t>
+          <t>146,601</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,66 +1283,66 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,112</t>
+          <t>30,450</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>30,676</t>
+          <t>4,943</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>147,686</t>
+          <t>9,045</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>13,410</t>
+          <t>13,312</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>31,057</t>
+          <t>30,829</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1425,56 +1425,56 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,773</t>
+          <t>10,694</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>26,089</t>
+          <t>43,679</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>44,002</t>
+          <t>25,897</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,584</t>
+          <t>13,484</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1513,51 +1513,51 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,320</t>
+          <t>16,200</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,909</t>
+          <t>94,926</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>95,629</t>
+          <t>6,858</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,695</t>
+          <t>3,667</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1601,29 +1601,29 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>5,948</t>
+          <t>5,904</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>ENPH US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Enphase能源公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>8,057</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,44 +1635,44 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ENPH US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>Enphase能源公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,873</t>
+          <t>23,625</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,117</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,673</t>
+          <t>18,535</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>38,717</t>
+          <t>38,433</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>119,057,868</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
